--- a/data/projects/drum-spread/raw/드럼확산_샘플.xlsx
+++ b/data/projects/drum-spread/raw/드럼확산_샘플.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -698,12 +698,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -747,12 +747,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2027-03-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2027-03-17</t>
+          <t>2027-03-24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2027-03-24</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
